--- a/out/policy_events_2026-05-12.xlsx
+++ b/out/policy_events_2026-05-12.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>트럼프 내일 방중, 시진핑과 이란-관세 담판&amp;nbsp;&amp;nbsp;동아일보트럼프, 美 대법원 비난…오는 12일부터 기납 관세 환급(상보)&amp;nbsp;&amp;nbsp;연합인포맥스트럼프 '비상'…인플레, 관세, 전쟁에 과반이상 '부정' 평가&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>트럼프 내일 방중, 시진핑과 이란-관세 담판&amp;nbsp;&amp;nbsp;동아일보트럼프, 美 대법원 비난…오는 12일부터 기납 관세 환급(상보)&amp;nbsp;&amp;nbsp;연합인포맥스트럼프, 관세 무효화 판결 본인 임명 대법관 2명 실명 비난&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -952,22 +952,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>흔들리는 트럼프 관세 전략…500조 대미 투자 이대로 GO? - 머니투데이 - 머니투데이</t>
+          <t>미중 정상회담, '관세 휴전' 넘어 동북아·중동 정세 안정 '시험대' 될까 - 인천투데이</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>흔들리는 트럼프 관세 전략…500조 대미 투자 이대로 GO? - 머니투데이&amp;nbsp;&amp;nbsp;머니투데이</t>
+          <t>미중 정상회담, '관세 휴전' 넘어 동북아·중동 정세 안정 '시험대' 될까&amp;nbsp;&amp;nbsp;인천투데이</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 21:10:00 GMT</t>
+          <t>Mon, 11 May 2026 05:35:04 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5xeWE0SVo2QmtINENjT2ctamt4TnhjLVRFbmNiM1N0YWs4Y0FyMUxEQ1ByRk9lUlAzOEF2bHI1UUNZcnUwSGxwQllTZW9HVXJMNFJiZGdBR2YzOWlWYnE3SnRuTDJOejNBWmEwUnVRTUjSAXBBVV95cUxOcXlhNElaNkJrSDRDY09nLWpreE54Yy1URW5jYjNTdGFrOGNBcjFMRENQckZPZVJQMzhBdmxyNVFDWXJ1MEhscEJZU2VvR1VyTDRSYmRnQUdmMzlpVmJxN0p0bkwyTnozQVphMFJ1UU1I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5qMk1Uc0F1Zm5jTFFHdUJtUmJHVEY0M2FySmxxNWVZR3pnbE1CWmJKVFcxelNBN0g4MTZCOVpKRXhLODE0ODJDbDhncEZkdWhnNzYtamsteUZxOFZXUEd5VUk2cm94REpyUzlYdFVoTVg?oc=5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -989,22 +989,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>미중 정상회담, '관세 휴전' 넘어 동북아·중동 정세 안정 '시험대' 될까 - 인천투데이</t>
+          <t>트럼프-시진핑, 6차례 만나… ‘부산 휴전’ 관세-희토류 2라운드 - 동아일보</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>미중 정상회담, '관세 휴전' 넘어 동북아·중동 정세 안정 '시험대' 될까&amp;nbsp;&amp;nbsp;인천투데이</t>
+          <t>트럼프-시진핑, 6차례 만나… ‘부산 휴전’ 관세-희토류 2라운드&amp;nbsp;&amp;nbsp;동아일보</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 05:35:04 GMT</t>
+          <t>Mon, 11 May 2026 19:30:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5qMk1Uc0F1Zm5jTFFHdUJtUmJHVEY0M2FySmxxNWVZR3pnbE1CWmJKVFcxelNBN0g4MTZCOVpKRXhLODE0ODJDbDhncEZkdWhnNzYtamsteUZxOFZXUEd5VUk2cm94REpyUzlYdFVoTVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE83Qjl1NHhsNzlUWW9CcXY1U0hqNDAwTk1xNW5YOEdkNVREeFdUOXpUV05yMWg4X1YzOU9LN2R6RGZPa0FpVTA0dWYtaHRUbF8yVVBpMTZSbnUwa2dLUlM0bkZGY3lsSXpwWDl1OFR6UnBxY3PSAWZBVV95cUxNR2RZcGhwVllPQzFpamVwSHU4UGN0MmN6ekN0WHZhc3hrM1JYdzRZMGsxak0yUVl0VlNpeUg5OTlKNnN3cTkzbkp2SEdOdXRZR3hrMDNGR2dDenZfcTlmR05adDViS0E?oc=5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>트럼프-시진핑, 6차례 만나… ‘부산 휴전’ 관세-희토류 2라운드 - 동아일보</t>
+          <t>관세청, 의료용품 관세조사…‘매점 매석’ 대응 확대 - 데일리메디</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>트럼프-시진핑, 6차례 만나… ‘부산 휴전’ 관세-희토류 2라운드&amp;nbsp;&amp;nbsp;동아일보</t>
+          <t>관세청, 의료용품 관세조사…‘매점 매석’ 대응 확대&amp;nbsp;&amp;nbsp;데일리메디</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 19:30:00 GMT</t>
+          <t>Mon, 11 May 2026 11:12:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE83Qjl1NHhsNzlUWW9CcXY1U0hqNDAwTk1xNW5YOEdkNVREeFdUOXpUV05yMWg4X1YzOU9LN2R6RGZPa0FpVTA0dWYtaHRUbF8yVVBpMTZSbnUwa2dLUlM0bkZGY3lsSXpwWDl1OFR6UnBxY3PSAWZBVV95cUxNR2RZcGhwVllPQzFpamVwSHU4UGN0MmN6ekN0WHZhc3hrM1JYdzRZMGsxak0yUVl0VlNpeUg5OTlKNnN3cTkzbkp2SEdOdXRZR3hrMDNGR2dDenZfcTlmR05adDViS0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE83bklTRFVBX0szeXU4ZXRZUHdWV2Z5cEJYUG4zRkJKMXlTZnNSSXpoZlB3dVA5TDNKU1pYLXZvUHl1NG5HbERZdjJqdG5VM3VlQTdWa2tRdVpqd01acmo1S1VDOW81dzJj?oc=5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>관세청, 의료용품 관세조사…‘매점 매석’ 대응 확대 - 데일리메디</t>
+          <t>미중 정상회담에 쏠리는 눈…이란·관세·AI 논의 전망 - 블로터</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>관세청, 의료용품 관세조사…‘매점 매석’ 대응 확대&amp;nbsp;&amp;nbsp;데일리메디</t>
+          <t>미중 정상회담에 쏠리는 눈…이란·관세·AI 논의 전망&amp;nbsp;&amp;nbsp;블로터</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 11:12:00 GMT</t>
+          <t>Mon, 11 May 2026 17:04:30 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE83bklTRFVBX0szeXU4ZXRZUHdWV2Z5cEJYUG4zRkJKMXlTZnNSSXpoZlB3dVA5TDNKU1pYLXZvUHl1NG5HbERZdjJqdG5VM3VlQTdWa2tRdVpqd01acmo1S1VDOW81dzJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE90X1dxSS10dHItWGdJbHRfUm5rRDc5UnNCOElxYi1SazF2V3JzTzBvaHEtMW5xMGNybHd3enRzdGM5Z0ItUGZLblJfclYxZzJzVG51ZExGNERudFlWVUZqRUdNS09RTW1a0gFsQVVfeXFMUDJpUkhnUVpXeDA2cVdDcmw4Y3Y2U3pLU3VHZjdNd1FUWWpSaW5tOU1vS19VS093Y1UzV25PYU8yNVdRbkR6cndVNGhzbDV5Q0NPR0I1VGhPb2wwLU1NOGhmRlNMZ1V3Z1BrR1dN?oc=5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>미중 정상회담에 쏠리는 눈…이란·관세·AI 논의 전망 - 블로터</t>
+          <t>물가급등에 다급한 트럼프, 수입 소고기 관세 완화 - 헤럴드경제</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>미중 정상회담에 쏠리는 눈…이란·관세·AI 논의 전망&amp;nbsp;&amp;nbsp;블로터</t>
+          <t>물가급등에 다급한 트럼프, 수입 소고기 관세 완화&amp;nbsp;&amp;nbsp;헤럴드경제</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 17:04:30 GMT</t>
+          <t>Mon, 11 May 2026 23:14:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE90X1dxSS10dHItWGdJbHRfUm5rRDc5UnNCOElxYi1SazF2V3JzTzBvaHEtMW5xMGNybHd3enRzdGM5Z0ItUGZLblJfclYxZzJzVG51ZExGNERudFlWVUZqRUdNS09RTW1a0gFsQVVfeXFMUDJpUkhnUVpXeDA2cVdDcmw4Y3Y2U3pLU3VHZjdNd1FUWWpSaW5tOU1vS19VS093Y1UzV25PYU8yNVdRbkR6cndVNGhzbDV5Q0NPR0I1VGhPb2wwLU1NOGhmRlNMZ1V3Z1BrR1dN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFAySzVYM0hqb0Z1elJCU2hOZmlkbUhtZFpGdDRVQTdMX1BKZmZsVE55SkxuTkkySnBKVmZoTVpkRXBXX2JpSml1SmJvMUY1VUpFbGxjeFR3?oc=5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>물가급등에 다급한 트럼프, 수입 소고기 관세 완화 - 헤럴드경제</t>
+          <t>"트럼프, 쇠고기 수입관세 한시 인하 추진" - 이데일리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>물가급등에 다급한 트럼프, 수입 소고기 관세 완화&amp;nbsp;&amp;nbsp;헤럴드경제</t>
+          <t>"트럼프, 쇠고기 수입관세 한시 인하 추진"&amp;nbsp;&amp;nbsp;이데일리</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 23:14:00 GMT</t>
+          <t>Mon, 11 May 2026 19:12:33 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFAySzVYM0hqb0Z1elJCU2hOZmlkbUhtZFpGdDRVQTdMX1BKZmZsVE55SkxuTkkySnBKVmZoTVpkRXBXX2JpSml1SmJvMUY1VUpFbGxjeFR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNQU9BcEoycDZ1eEduVGlGLW1kVzdlSUx0LW92YWRnR0F3Z2huZEVfNnh4S3NFRGI4anJER1ZNRzBwdkNUVWhhX3Z0YnRURndZZWNNcjBVOWx1cUE3TTNtN01vdGdLdmdQRzJlUjZNa2ticFllZFdOUGt5NUUzM1hVNg?oc=5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1174,22 +1174,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"트럼프, 쇠고기 수입관세 한시 인하 추진" - 이데일리</t>
+          <t>관세·이란 전쟁…협상력 잃은 트럼프, 시진핑 만나도 돌파구 없을 듯 - 프레시안</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>"트럼프, 쇠고기 수입관세 한시 인하 추진"&amp;nbsp;&amp;nbsp;이데일리</t>
+          <t>관세·이란 전쟁…협상력 잃은 트럼프, 시진핑 만나도 돌파구 없을 듯&amp;nbsp;&amp;nbsp;프레시안</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 19:12:33 GMT</t>
+          <t>Mon, 11 May 2026 08:17:51 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNQU9BcEoycDZ1eEduVGlGLW1kVzdlSUx0LW92YWRnR0F3Z2huZEVfNnh4S3NFRGI4anJER1ZNRzBwdkNUVWhhX3Z0YnRURndZZWNNcjBVOWx1cUE3TTNtN01vdGdLdmdQRzJlUjZNa2ticFllZFdOUGt5NUUzM1hVNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBzOEs1VWJqZW4yMklVYkFvMm5IcTAxbDBtVnpIU3ZycGppNTdheW1OTXdWbVRpb3o2YzkwWG0ycDBqSlBYNENITzhGYTdRbzJDWGV5amRwbGpkLVdjOEY5UjdoUm9QS1ZULXRv?oc=5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1211,22 +1211,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>관세·이란 전쟁…협상력 잃은 트럼프, 시진핑 만나도 돌파구 없을 듯 - 프레시안</t>
+          <t>나이키, 트럼프 관세 환급금 두고 소비자 집단소송 직면… "가격 인상분 반환하라“ - 글로벌이코노믹</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>관세·이란 전쟁…협상력 잃은 트럼프, 시진핑 만나도 돌파구 없을 듯&amp;nbsp;&amp;nbsp;프레시안</t>
+          <t>나이키, 트럼프 관세 환급금 두고 소비자 집단소송 직면… "가격 인상분 반환하라“&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 11 May 2026 08:17:51 GMT</t>
+          <t>Mon, 11 May 2026 03:54:58 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBzOEs1VWJqZW4yMklVYkFvMm5IcTAxbDBtVnpIU3ZycGppNTdheW1OTXdWbVRpb3o2YzkwWG0ycDBqSlBYNENITzhGYTdRbzJDWGV5amRwbGpkLVdjOEY5UjdoUm9QS1ZULXRv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPZ0tkRE5meDRhUC1lbk5LalVUVElYSVl0TVRCMEFSaFRCSUxpUEdSSzdSX0w0bWRoUGlYUFpOU2VicDdGZHd4d1ZUSkJ2VXdDSFFJVUVuekppRUdEdTl5aDMtOFd2dVlTeUNNYUFfUkRBRlMtUno3QkUzWlFCNVRIeHdmZlliSlBM?oc=5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
